--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/region-aysen-del-general-carlos-ibanez-del-campo.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/region-aysen-del-general-carlos-ibanez-del-campo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5019-215-CM26</t>
+          <t>1286962-6-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>65.072.937-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Corporación de Deportes y Recreación de la Municipalidad de Aysén</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,681 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>1049.58</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4609-19-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ene-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>29333.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1195-72-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>24276</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5038-19-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.253.100-0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>33290.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3622-27-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.253.500-6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>13854.46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3951-121-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.974.700-3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>894.88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2713-309-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>44387</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1195-340-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>7090.02</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>734-761-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>293475.42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1195-536-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>6806.42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1182705-225-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>65.199.131-5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>33834.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5019-215-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>65.224.300-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>1267.85</v>
       </c>
     </row>
